--- a/healthcare_surveys/004_healthcare_leadership_inclusivity_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/004_healthcare_leadership_inclusivity_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -619,8 +619,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,12 +648,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_2.1,_'name':_'strongly_supportive',_'label':_'strongly_supportive'}</t>
+          <t>strongly_supportive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 2.1, 'name': 'strongly_supportive', 'label': 'Strongly Supportive'}</t>
+          <t>Strongly Supportive</t>
         </is>
       </c>
     </row>
@@ -665,12 +665,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'2.1.1',_'name':_'somewhat_supportive',_'label':_'somewhat_supportive'}</t>
+          <t>somewhat_supportive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '2.1.1', 'name': 'somewhat_supportive', 'label': 'Somewhat Supportive'}</t>
+          <t>Somewhat Supportive</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'2.1.2',_'name':_'neither',_'label':_'neither'}</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '2.1.2', 'name': 'neither', 'label': 'Neither'}</t>
+          <t>Neither</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_3.1,_'name':_'none',_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 3.1, 'name': 'none', 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3.2,_'name':_'some_barriers',_'label':_'some'}</t>
+          <t>some</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3.2, 'name': 'some_barriers', 'label': 'Some'}</t>
+          <t>Some</t>
         </is>
       </c>
     </row>
@@ -733,12 +733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3.3,_'name':_'many_barriers',_'label':_'many'}</t>
+          <t>many</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3.3, 'name': 'many_barriers', 'label': 'Many'}</t>
+          <t>Many</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4.1,_'name':_'no_ideas',_'label':_'no_ideas'}</t>
+          <t>no_ideas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4.1, 'name': 'no_ideas', 'label': 'No Ideas'}</t>
+          <t>No Ideas</t>
         </is>
       </c>
     </row>
@@ -767,12 +767,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4.2,_'name':_'some_ideas',_'label':_'some_ideas'}</t>
+          <t>some_ideas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4.2, 'name': 'some_ideas', 'label': 'Some Ideas'}</t>
+          <t>Some Ideas</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4.3,_'name':_'many_ideas',_'label':_'many_ideas'}</t>
+          <t>many_ideas</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4.3, 'name': 'many_ideas', 'label': 'Many Ideas'}</t>
+          <t>Many Ideas</t>
         </is>
       </c>
     </row>
